--- a/corrections.xlsx
+++ b/corrections.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robinpfaff/Desktop/Master_Thesis_public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EBB24B4-C381-644E-B535-CCC2CF2372B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{335762D3-A225-1849-958E-687A8A3BF546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="3020" windowWidth="29080" windowHeight="19380" xr2:uid="{BCDCC95F-E5FF-4D43-82C5-79246A9B99AA}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="20160" windowHeight="21800" xr2:uid="{BCDCC95F-E5FF-4D43-82C5-79246A9B99AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="94">
   <si>
     <t>Required amendments Thesis Robin Pfaff</t>
   </si>
@@ -72,9 +71,6 @@
     <t>Reference details (use of initials in in-text citations)</t>
   </si>
   <si>
-    <t>not needed</t>
-  </si>
-  <si>
     <t>Comment</t>
   </si>
   <si>
@@ -131,9 +127,6 @@
   </si>
   <si>
     <t>https://apastyle.apa.org/style-grammar-guidelines/references/examples/webpage-website-references</t>
-  </si>
-  <si>
-    <t>(Dice, 𝐿𝑊𝐵𝐶𝐸, 𝐿𝑐)</t>
   </si>
   <si>
     <r>
@@ -341,13 +334,532 @@
   </si>
   <si>
     <t>moved from section 2.3 to after first paragraph in section 2.2</t>
+  </si>
+  <si>
+    <t>28 (Table 2)</t>
+  </si>
+  <si>
+    <t>moved up one paragraph to be placed immediately after first mention</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">canopy extents visible in orthomosaics </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(Figure 16)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>canopy extents visible in orthomosaics.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">removed mention in methods part for results figure. </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Alternatively to the F1 score, accuracy can also be used, which is defined as:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> {equation 7}</t>
+    </r>
+  </si>
+  <si>
+    <t>Rebecca Campbell</t>
+  </si>
+  <si>
+    <t>Anonymous Examinor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I did not move eqation 7 to the methods, since it describes accuracy. This is a metric I do not use to assess my results, but only explain to compare it to other studies that use this evaluation metric. Therefore, I kept it in the discussion.  However, I embedded the equation within the paragraph, rather than at the end of it. </t>
+  </si>
+  <si>
+    <t>See next point</t>
+  </si>
+  <si>
+    <t>Moved  following sections to new literature review chapter:
+- Plant-level Symptoms of Myrtle Rust
+- Management and Mitigation Strategies
+- Current Mapping of S. maire
+- Deep Learning for Species Mapping
+- 2D Semantic Segmentation
+- 3D Instance Segmentation and Point Cloud Processing</t>
+  </si>
+  <si>
+    <r>
+      <t>Revised structure and added a summary sentence to "</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Consequences of Myrtle Rust for New Zealand" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>section to give an info around plant level symptoms in introduction (which were moved to literature review).</t>
+    </r>
+  </si>
+  <si>
+    <t>Scope and Novelty</t>
+  </si>
+  <si>
+    <t>Research Aims and Scope</t>
+  </si>
+  <si>
+    <t>changed section title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in (renamed) section Research Aims and Scope, added this introductory paragraph which also replaces the final paragraph. </t>
+  </si>
+  <si>
+    <t>The research scope encompasses four urban forest reserves in the North Island of New Zealand with known {{&lt; acr SM &gt;}} populations. By explicitly testing on a rare species in dense, biodiverse forests rather than on readily detectable canopy dominants, this thesis explores operational capabilities and limitations of current {{&lt; acr UAV &gt;}}-{{&lt; acr DL &gt;}} approaches for conservation applications.</t>
+  </si>
+  <si>
+    <t>added new summary section to introduction to introduce remote sensing/deep-learning</t>
+  </si>
+  <si>
+    <t>invalid critique; not needed</t>
+  </si>
+  <si>
+    <t>A. psidii infects actively growing tissue and can cause yellow pustules, necrotic lesions,
+shoot dieback, and defoliation (Boufleur et al., 2023). This reduces regeneration and increases
+mortality risk in susceptible Myrtaceae (Fensham &amp; Radford-Smith, 2021)</t>
+  </si>
+  <si>
+    <t>The need for automated S. maire mapping is driven by the species’ ecological importance,
+its vulnerability to myrtle rust, and the practical limits of field-based monitoring. This thesis
+tests whether current unmanned aerial vehicle (UAV)-deep learning approaches can support
+conservation monitoring of a rare, morphologically subtle species in dense, biodiverse native
+forest. Accordingly, the research focuses on four urban forest reserves in the North Island of
+New Zealand with known S. maire populations to explicitly evaluate operational capabilities and
+limitations when detecting non-dominant canopy species.</t>
+  </si>
+  <si>
+    <t>## UAV-based Deep Learning for Plant Species Mapping
+Deep learning has transformed species mapping from remote sensing by enabling models to
+learn hierarchical spectral–spatial features directly from remotely sensed imagery and structural
+features from 3D point clouds, supporting end-to-end detection and classification workflows
+(LeCun et al., 2015; L. Zhong et al., 2024). Convolutional neural network (CNN) and more
+recent encoder–decoder segmentation architectures applied to high-resolution UAV and satellite
+imagery can capture fine-grained canopy texture and spectral signals that are often indicative of species identity at the crown and sub-crown scales (Kattenborn et al., 2019; Lobo Torres et al.,
+2020). Complementary 3D approaches that operate on LiDAR-derived point clouds (including
+PointNet++ and voxel-based models) extract crown geometry, vertical structure, and other
+structural traits to distinguish species with subtle foliar differences (Briechle et al., 2020; Qi et al.,
+2017). Furthermore, multimodal approaches fuse 2D with 3D data to improve discrimination in
+complex, multi-species canopies, though they introduce challenges around sensor co-registration
+and increased computational complexity (Briechle et al., 2020; L. Zhong et al., 2024).
+Despite these advances, operational deployment faces constraints including limited instances
+for rare species, strong class imbalance, site-to-site transferability, and the need for careful
+validation against ground truth. Given the complexity of fusing multimodal data, this thesis
+focuses on single-source data, while treating the 3D workflow as an exploratory complement to
+the primary 2D approach.</t>
+  </si>
+  <si>
+    <t>established RQ as a abbreviation and use it to link to research questions across  methods chapter</t>
+  </si>
+  <si>
+    <t>Added this paragarph at the start and structured all sections under these 3 main headers</t>
+  </si>
+  <si>
+    <t>New sub-section to justify the exploratory LiDAR approach</t>
+  </si>
+  <si>
+    <t>slight adjustments to headings</t>
+  </si>
+  <si>
+    <r>
+      <t>UAV-RGB and MS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> Data Collection 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve">UAV-LiDAR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve">Data Collection </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Data Processing and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>Analysis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Dataset</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> Generation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Architecture
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>Inference and Evaluation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">UAV-RGB and MS </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Acquisition
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UAV-LiDAR</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Acquisition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Data Processing and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Model Development
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dataset</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Preparation
+Model </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Architecture
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Evaluation and Analysis</t>
+    </r>
+  </si>
+  <si>
+    <t>added new section</t>
+  </si>
+  <si>
+    <t>Future Work
+Several lines of work follow directly from the limitations identified above and from the LiDAR
+experiments. First, future research should initially focus on improving the identification of S.
+maire before attempting direct disease detection. This requires larger and more diverse training
+samples drawn from additional sites and seasons (for example inclusion of natural old-growth
+swamp, different urban parks, replanted sites and remnant trees) to improve representativeness.
+In cases where disease detection is the priority, targeted acquisitions during the March–April
+symptom peak are recommended.
+Second, LiDAR-based methods require further algorithmic development and domain-adaptive
+training: both TreeLearn and Treeiso would benefit from fine-tuning on representative native-
+forest UAV/TLS datasets. Exploring higher-density or full-waveform sensors could also improve
+structural signal for both instance segmentation and health assessment.
+Third, multi-modal fusion warrants focused development: combining spectral information from
+MS orthomosaics with structural data from LiDAR point clouds (for example by projecting MS
+bands onto segmented tree point clouds) is a promising avenue shown to be viable in prior work
+(Briechle et al., 2020).
+Finally, operational deployment should prioritise integration with SDM outputs to guide targeted
+UAV surveys and standardise radiometric calibration workflows across sites to reduce multi-site
+generalisation issues.</t>
+  </si>
+  <si>
+    <t>I went through all abbreviation terms and this is the only I found that wasn't consistently applied.</t>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>Dice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 𝐿𝑊𝐵𝐶𝐸, 𝐿𝑐)</t>
+    </r>
+  </si>
+  <si>
+    <t>Scope and justification of the LiDAR component
+The LiDAR work in this thesis is presented as a targeted, exploratory component intended to assess whether 3D tree-segmentation outputs could potentially complement the raster-based deep learning workflow. Due to operational constraints (different oblique flight counts and resulting point-density variation), time limitations and initial segmentation quality, the LiDAR analysis was scoped to a pilot evaluation and qualitative assessment rather than a full quantitative integration with the U-Net experiments. Hence, the scope of the LiDAR component and its results are exploratory: useful for identifying promising directions, but not used as a primary source for the main comparative model evaluations. Recommendations for deeper, quantitative follow-up work are given in the discussion.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">his thesis addresses four research questions </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(RQs)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: (1) Can</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">his thesis addresses four research questions: (1) Can </t>
+  </si>
+  <si>
+    <t>This chapter describes the methodological approach used to address the thesis research questions, and is organised into four parts: (1) experimental design and data collection, (2) data processing and model development, (3) evaluation and analysis, and (4) exploratory LiDAR tree segmentation. The experiments were designed to investigate detection accuracy, the contribution of different sensor and band combinations, and model generalisability across sites.</t>
+  </si>
+  <si>
+    <t>The annotator first examined unambiguous S. maire individuals to establish their characteristic visual appearance.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The annotator first examined unambiguous S. maire individuals to establish their characteristic visual appearance </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Figure 10a)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>31 (Figure 10)</t>
+  </si>
+  <si>
+    <t>moved directly to after section where ist mentioned first.</t>
+  </si>
+  <si>
+    <t>39 (Figure 13)</t>
+  </si>
+  <si>
+    <r>
+      <t>(using only the sun sensor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>; Table 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>(using only the sun sensor).</t>
+  </si>
+  <si>
+    <t>removed this first mention of table 3 as ist not necessary and I want to keep the position in a later section where it is mentioned again.</t>
+  </si>
+  <si>
+    <t>44 (after S6)</t>
+  </si>
+  <si>
+    <t>Annex B</t>
+  </si>
+  <si>
+    <t>Order of Sfig 5-9 adjusted in annex B to be in order of first mention.</t>
+  </si>
+  <si>
+    <t>Separated S-Figs from S-Tables</t>
+  </si>
+  <si>
+    <t>Order of Stbl 2-2 adjusted in annex B to be in order of first mention. And added headers.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -407,8 +919,20 @@
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow (Body)"/>
     </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow (Body)"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -427,6 +951,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -441,33 +977,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -804,228 +1368,596 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4EAE2CD-D0EE-2A4C-AA33-5D2F1BB6AF10}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="68.6640625" customWidth="1"/>
-    <col min="2" max="2" width="25.33203125" style="11" customWidth="1"/>
-    <col min="3" max="3" width="50.5" customWidth="1"/>
-    <col min="4" max="4" width="49" customWidth="1"/>
-    <col min="5" max="5" width="53" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="2" max="2" width="45.5" customWidth="1"/>
+    <col min="3" max="3" width="25.33203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="53" customWidth="1"/>
+    <col min="5" max="5" width="82.83203125" customWidth="1"/>
+    <col min="6" max="6" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="27" x14ac:dyDescent="0.35">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="C3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="19"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="8">
+        <v>18</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="19"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8">
+        <v>23</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="19"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="8">
+        <v>56</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="19"/>
+      <c r="B8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="69" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="19"/>
+      <c r="B9" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="9"/>
+    </row>
+    <row r="10" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="19"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="19"/>
+      <c r="B11" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="8">
+        <v>12</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A12" s="19"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A13" s="19"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="19"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="19"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="8">
+        <v>37</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A16" s="19"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="8">
+        <v>29</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="14"/>
+    </row>
+    <row r="17" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="19"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" s="19"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A19" s="19"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A20" s="19"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E20" s="20"/>
+      <c r="F20" s="14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A21" s="19"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" s="20"/>
+      <c r="F21" s="14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="19"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="20"/>
+      <c r="F22" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="19"/>
+      <c r="B23" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="E23" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="19"/>
+      <c r="B24" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" s="14"/>
+    </row>
+    <row r="26" spans="1:6" ht="55" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="19"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="19"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="119" x14ac:dyDescent="0.2">
+      <c r="A28" s="19"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="328" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="19"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="19"/>
+      <c r="B30" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="19"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="199" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="19"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="174" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="19"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="331" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="19"/>
+      <c r="B34" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="8"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="19"/>
+      <c r="B35" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="8">
+        <v>35</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40" s="4"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D41">
+        <v>2</v>
+      </c>
+      <c r="E41" s="4"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D42">
+        <v>3</v>
+      </c>
+      <c r="E42" s="4"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D43">
+        <v>4</v>
+      </c>
+      <c r="E43" s="4">
+        <v>34</v>
+      </c>
+      <c r="F43">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D44">
+        <v>5</v>
+      </c>
+      <c r="E44" s="4">
+        <v>60</v>
+      </c>
+      <c r="F44">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D45">
+        <v>6</v>
+      </c>
+      <c r="E45" s="4">
+        <v>44</v>
+      </c>
+      <c r="F45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D46">
+        <v>7</v>
+      </c>
+      <c r="E46" s="4">
+        <v>46</v>
+      </c>
+      <c r="F46">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D47">
+        <v>8</v>
+      </c>
+      <c r="E47" s="4">
+        <v>48</v>
+      </c>
+      <c r="F47">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D48">
+        <v>9</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F48">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D49">
         <v>10</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
-      <c r="B5" s="11">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
-      <c r="B6" s="11">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
-      <c r="B7" s="11">
-        <v>56</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="85" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
-      <c r="B10" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="11">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="64" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="51" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="48" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="11">
-        <v>35</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" t="s">
-        <v>25</v>
-      </c>
+      <c r="E49" s="4"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A25:A35"/>
+    <mergeCell ref="A4:A24"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F4" r:id="rId1" xr:uid="{5C22194B-0137-0242-99DF-BFDFA382D1D1}"/>
-    <hyperlink ref="F8" r:id="rId2" xr:uid="{B6DFF4AB-7EDB-FB4B-B981-8E5175E5D5CB}"/>
+    <hyperlink ref="G4" r:id="rId1" xr:uid="{5C22194B-0137-0242-99DF-BFDFA382D1D1}"/>
+    <hyperlink ref="G8" r:id="rId2" xr:uid="{B6DFF4AB-7EDB-FB4B-B981-8E5175E5D5CB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
